--- a/data/donations.xlsx
+++ b/data/donations.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -569,6 +569,53 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ASTRO-1785079329</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26 20:52:09</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>hr@gmail.com</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Pending PDF Report</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
